--- a/temp/MACRO_VISA_20220525.xlsx
+++ b/temp/MACRO_VISA_20220525.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-1200</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-1200,0</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>-701084.9300000001</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-701084,93</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -513,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>009216* WWW.E-FARMACITY.COM Cuota 04/06</t>
+          <t>WWW.E-FARMACITY.COM Cuota 04/06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>865</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>865,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -538,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>546391K MERCADO LIBR*CECILIAMARIE</t>
+          <t>MERCADO LIBR*CECILIAMARIE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>7775.28</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7775,28</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -563,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>292937K MERCADO LIBR*FERRETCORDOB</t>
+          <t>MERCADO LIBR*FERRETCORDOB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>8760</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8760,0</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -588,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>328861K MERCADO LIBR*FARMACITY</t>
+          <t>MERCADO LIBR*FARMACITY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -596,12 +606,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1935.26</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1935,26</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -613,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>714057* MERCPAG*AGUA PUREZA Cuota 07/18</t>
+          <t>MERCPAG*AGUA PUREZA Cuota 07/18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,12 +633,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1696.38</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1696,38</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -638,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>003619* MERCADOPAGO*DINATECHSA Cuota 07/12</t>
+          <t>MERCADOPAGO*DINATECHSA Cuota 07/12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -646,12 +660,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>5758.25</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5758,25</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -663,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>448754* ON FIT Cuota 06/18</t>
+          <t>ON FIT Cuota 06/18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -671,12 +687,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>7290</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7290,0</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -688,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>412588* MERCADOPAGO*MERCADOL Cuota 05/06</t>
+          <t>MERCADOPAGO*MERCADOL Cuota 05/06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -696,12 +714,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>4633.33</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4633,33</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -713,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>000181* VITAL SUPERMAYORISTA Cuota 03/12</t>
+          <t>VITAL SUPERMAYORISTA Cuota 03/12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -721,12 +741,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1999</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1999,0</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -738,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>004092* WWW.MOOVBYDEXTER.COM.AR Cuota 02/03</t>
+          <t>WWW.MOOVBYDEXTER.COM.AR Cuota 02/03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -746,12 +768,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>9997.66</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9997,66</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -763,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>005412* WWW.DEXTER.COM.AR Cuota 02/03</t>
+          <t>WWW.DEXTER.COM.AR Cuota 02/03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -771,12 +795,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>23664.33</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>23664,33</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -788,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>278594K MERCADOPAGO*AXIONENERGY</t>
+          <t>MERCADOPAGO*AXIONENERGY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,12 +822,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1899.4</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1899,4</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -813,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>187312K MERCADO LIBR*PERSONAL</t>
+          <t>MERCADO LIBR*PERSONAL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -821,12 +849,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>600</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>600,0</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -838,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>607909K MERCADO LIBR*PERSONAL</t>
+          <t>MERCADO LIBR*PERSONAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -846,12 +876,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>600</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>600,0</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -863,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>608559K MERCADO LIBR*PERSONAL</t>
+          <t>MERCADO LIBR*PERSONAL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -871,12 +903,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>600</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>600,0</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -888,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>899379K MERCADO LIBR*MCDONALDS</t>
+          <t>MERCADO LIBR*MCDONALDS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -896,12 +930,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>7110</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7110,0</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -913,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>757626* MERCADO LIBR*ILGATTO</t>
+          <t>MERCADO LIBR*ILGATTO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -921,12 +957,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>15700</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>15700,0</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -938,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>489939* VEA SM 700</t>
+          <t>VEA SM 700</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -946,12 +984,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1390.48</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1390,48</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -963,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002852* CARNICERIA EL CHINO 3503</t>
+          <t>CARNICERIA EL CHINO 3503</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -971,12 +1011,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>15373</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>15373,0</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -988,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>490032* VEA SM 700</t>
+          <t>VEA SM 700</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -996,12 +1038,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>2767.15</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2767,15</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>341750* Rebelde by Kentucky</t>
+          <t>Rebelde by Kentucky</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1021,12 +1065,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>7960</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7960,0</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>814137K MERCADO LIBR*THOMAS</t>
+          <t>MERCADO LIBR*THOMAS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1046,12 +1092,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>2200</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2200,0</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>360317K MERCADO LIBR*SUPERDIA</t>
+          <t>MERCADO LIBR*SUPERDIA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1071,12 +1119,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>405.6</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>405,6</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>369859K MERCADO LIBR*HELADOSCANN</t>
+          <t>MERCADO LIBR*HELADOSCANN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1096,12 +1146,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>1700</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1700,0</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>303982K MERCADO LIBR*OPEN25</t>
+          <t>MERCADO LIBR*OPEN25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1121,12 +1173,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>490</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>490,0</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>587724K MERCADO LIBR*SUPERDIA</t>
+          <t>MERCADO LIBR*SUPERDIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1146,12 +1200,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>4002.3</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4002,3</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>000621* HERTZ ARGENTINA 3109</t>
+          <t>HERTZ ARGENTINA 3109</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1171,12 +1227,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>12712.79</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>12712,79</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>032848* PERSONAL FLOW 000000058156976</t>
+          <t>PERSONAL FLOW 000000058156976</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1196,12 +1254,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>3561.99</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3561,99</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>000001* EDENOR 000007691385963</t>
+          <t>EDENOR 000007691385963</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1221,12 +1281,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>599.47</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>599,47</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>344779* RAPANUI</t>
+          <t>RAPANUI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1246,12 +1308,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>1350</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1350,0</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>643070* AUTOSERVICIO ELIE</t>
+          <t>AUTOSERVICIO ELIE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1271,12 +1335,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>395</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>395,0</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>687477* HORMANN MONTARCE SA</t>
+          <t>HORMANN MONTARCE SA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1296,12 +1362,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>5861.9</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>5861,9</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1381,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>002294* HALABI ROBERTO ADOLF 8536</t>
+          <t>HALABI ROBERTO ADOLF 8536</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1321,12 +1389,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>12550</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>12550,0</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>313717* MATTONE</t>
+          <t>MATTONE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1346,12 +1416,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>11760</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>11760,0</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1435,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>008618* HORMANN MONTARCE SA</t>
+          <t>HORMANN MONTARCE SA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1371,12 +1443,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>1191</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1191,0</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>008632* HORMANN MONTARCE SA</t>
+          <t>HORMANN MONTARCE SA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1396,12 +1470,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>1166.98</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1166,98</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1489,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>008633* HORMANN MONTARCE SA</t>
+          <t>HORMANN MONTARCE SA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1421,12 +1497,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>732</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>732,0</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1516,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>005585Q NETFLIX.COM 6865726284498327</t>
+          <t>NETFLIX.COM 6865726284498327</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1446,12 +1524,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>1199</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1199,0</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>718898K MERCADO LIBR*FARMACIA</t>
+          <t>MERCADO LIBR*FARMACIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1471,12 +1551,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>1640</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1640,0</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>077377* YPF PINAMAR</t>
+          <t>YPF PINAMAR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1496,12 +1578,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>5199.6</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5199,6</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1597,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>395652* GRILLER</t>
+          <t>GRILLER</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1521,12 +1605,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>21450</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>21450,0</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1624,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>400119K MERCADO LIBR*FERBESTEIRO</t>
+          <t>MERCADO LIBR*FERBESTEIRO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1546,12 +1632,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>5600</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5600,0</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1651,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>775359K MERCADO LIBR*ESTRAVASALE</t>
+          <t>MERCADO LIBR*ESTRAVASALE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1571,12 +1659,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>980</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>980,0</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1678,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>609729* HORMANN MONTARCE SA</t>
+          <t>HORMANN MONTARCE SA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1596,12 +1686,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>8172.24</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8172,24</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1705,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>002433* LA CELINA SUR 8131</t>
+          <t>LA CELINA SUR 8131</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1621,12 +1713,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>14620</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>14620,0</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1732,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>985415* MERCADO LIBR*CATYCAN</t>
+          <t>MERCADO LIBR*CATYCAN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1646,12 +1740,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>8934.75</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8934,75</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1759,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>224574* EST DE SERV SAN LUIS</t>
+          <t>EST DE SERV SAN LUIS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1671,12 +1767,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1102</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1102,0</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>009358* AXION GUTIERREZ</t>
+          <t>AXION GUTIERREZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1696,12 +1794,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>5800.5</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5800,5</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1813,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>765962 OF USD 11,30</t>
+          <t>OF USD 11,30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1721,12 +1821,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>11.3</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>11,3</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1840,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>541642* MERCADO LIBR*VENESTORE</t>
+          <t>MERCADO LIBR*VENESTORE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1746,12 +1848,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>2809.96</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2809,96</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1867,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>389699K MERCADO LIBR*FARMACITY</t>
+          <t>MERCADO LIBR*FARMACITY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1771,12 +1875,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>7080</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7080,0</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1894,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>439325K MERCADO LIBR*SUPERDIA</t>
+          <t>MERCADO LIBR*SUPERDIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1796,12 +1902,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>417.33</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>417,33</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1921,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>576795K MERCADO LIBR*FARMACITY</t>
+          <t>MERCADO LIBR*FARMACITY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1821,12 +1929,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>1544.45</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1544,45</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1948,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>421663K MERCADO LIBR*VITALMAYORIS</t>
+          <t>MERCADO LIBR*VITALMAYORIS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1846,12 +1956,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>66808.69</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>66808,69</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1975,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>878237* VEA SM 700</t>
+          <t>VEA SM 700</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1871,12 +1983,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>10544.54</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>10544,54</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1888,7 +2002,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>878365* VEA SM 700 Cuota 01/12</t>
+          <t>VEA SM 700 Cuota 01/12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1896,12 +2010,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>12374.98</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>12374,98</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1913,7 +2029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>878366* VEA SM 700 Cuota 01/12</t>
+          <t>VEA SM 700 Cuota 01/12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1921,12 +2037,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>9562.530000000001</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>9562,53</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1938,7 +2056,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>878439* VEA SM 700</t>
+          <t>VEA SM 700</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1946,12 +2064,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>2514.29</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2514,29</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1963,7 +2083,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>878052* VEA SM 700</t>
+          <t>VEA SM 700</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1971,12 +2091,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>4882.7</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4882,7</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2110,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>959705K MERCADO LIBR*FERRETCORDOB</t>
+          <t>MERCADO LIBR*FERRETCORDOB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1996,12 +2118,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>11220</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>11220,0</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2137,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>425330* HOME HOTEL BUENOS AIRE</t>
+          <t>HOME HOTEL BUENOS AIRE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2021,12 +2145,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>5500</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>5500,0</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2164,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>878276* VEA SM 700</t>
+          <t>VEA SM 700</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2046,12 +2172,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>1036.88</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1036,88</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2191,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>576364* ATTE.PIZZERIA NAPOLETA</t>
+          <t>ATTE.PIZZERIA NAPOLETA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2071,12 +2199,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>28180</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>28180,0</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2218,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>725961K MERCADO LIBR*REPUESTOSLAC</t>
+          <t>MERCADO LIBR*REPUESTOSLAC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2096,12 +2226,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>36400</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>36400,0</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2245,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>252999* METROGAS SA DEB 040000136346</t>
+          <t>METROGAS SA DEB 040000136346</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2121,12 +2253,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>344.6</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>344,6</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2272,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>356488K MERCADO LIBR*REPUESTOSLAC</t>
+          <t>MERCADO LIBR*REPUESTOSLAC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2146,12 +2280,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>22000</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22000,0</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2299,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>201391K MERCADO LIBR*THOMAS</t>
+          <t>MERCADO LIBR*THOMAS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2171,12 +2307,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>1720</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1720,0</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2326,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>216133K MERCADO LIBR*SUPERDIA</t>
+          <t>MERCADO LIBR*SUPERDIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2196,12 +2334,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>792.5</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>792,5</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2353,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>034462K MERCADO LIBR*ALARABE</t>
+          <t>MERCADO LIBR*ALARABE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2221,12 +2361,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>13706</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>13706,0</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2380,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>075918K MERCADO LIBR*HELADOSITALI</t>
+          <t>MERCADO LIBR*HELADOSITALI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2246,12 +2388,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>5400</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>5400,0</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2407,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>787692K MERCADO LIBR*LABIRRABARCO</t>
+          <t>MERCADO LIBR*LABIRRABARCO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2271,12 +2415,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>7280</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>7280,0</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2434,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>793164K MERCADO LIBR*LABIRRABARCO</t>
+          <t>MERCADO LIBR*LABIRRABARCO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2296,12 +2442,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>1400</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1400,0</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2461,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>000160K MERCADO LIBR*THOMAS</t>
+          <t>MERCADO LIBR*THOMAS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2321,12 +2469,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>9030</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>9030,0</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2488,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>723585V Spotify P1FA6BC5 P1FA6BC536</t>
+          <t>Spotify P1FA6BC5 P1FA6BC536</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2346,12 +2496,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>389</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>389,0</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2515,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>510275* EXPERTA SEGUR 0000006884833-015-003</t>
+          <t>EXPERTA SEGUR 0000006884833-015-003</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2371,12 +2523,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>173</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>173,0</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2542,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>510274* EXPERTA SEGUR 0000006884832-015-002</t>
+          <t>EXPERTA SEGUR 0000006884832-015-002</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2396,12 +2550,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>845</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>845,0</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2569,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>249542K MERPAGO*PIAF</t>
+          <t>MERPAGO*PIAF</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2421,12 +2577,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>1900</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1900,0</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2596,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>329101* VEA SM 700</t>
+          <t>VEA SM 700</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2446,12 +2604,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>17340.08</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>17340,08</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2623,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>329102* VEA SM 700</t>
+          <t>VEA SM 700</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2471,12 +2631,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>11430.58</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>11430,58</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2650,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>500750K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2496,12 +2658,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>12263.15</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>12263,15</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2685,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>6847.7</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6847,7</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2712,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>24.4</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>24,4</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2739,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>127.04</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>127,04</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2766,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>23.98</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>23,98</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2793,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>7.78</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>7,78</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2646,12 +2820,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>251.79</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>251,79</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2847,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>81.69</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>81,69</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2874,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>590.8</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>590,8</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2901,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>1600.81</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1600,81</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
